--- a/docx_templates/relatorio_inadimplencia_modelo.xlsx
+++ b/docx_templates/relatorio_inadimplencia_modelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabm\OneDrive\Documentos\projeto_ativuz\docx_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB79AD5A-1B82-4316-B495-9FBADF5EBE51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F9C9A1-609A-4A28-8E78-7CF29066936B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -180,7 +180,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\R\$\ #,##0.00"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,6 +270,19 @@
       <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFAAAAAA"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -377,7 +390,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -425,15 +438,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF1A3A5C"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color rgb="FFBDBDBD"/>
@@ -446,7 +450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -457,7 +461,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -473,7 +476,6 @@
     <xf numFmtId="164" fontId="9" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -531,89 +533,71 @@
     <xf numFmtId="0" fontId="11" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -918,107 +902,86 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N60"/>
+  <dimension ref="B1:I60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="56" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="2" max="2" width="40.6640625" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="3" customWidth="1"/>
+    <col min="9" max="9" width="29.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:14" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="39" t="s">
+    <row r="1" spans="2:9" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-    </row>
-    <row r="3" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="34" t="s">
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+    </row>
+    <row r="3" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34"/>
-    </row>
-    <row r="4" spans="1:14" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="41" t="s">
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+    </row>
+    <row r="4" spans="2:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43" t="s">
+      <c r="C4" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="43"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="45" t="s">
+      <c r="D4" s="40"/>
+      <c r="E4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="46"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="48" t="s">
+      <c r="F4" s="32"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="49"/>
-      <c r="M4" s="49"/>
-      <c r="N4" s="50"/>
-    </row>
-    <row r="5" spans="1:14" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="51">
-        <f>COUNTA(B9:B57)</f>
+      <c r="I4" s="45"/>
+    </row>
+    <row r="5" spans="2:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="50">
+        <f>COUNTA(C9:C57)</f>
         <v>5</v>
       </c>
-      <c r="D5" s="52"/>
-      <c r="E5" s="53">
+      <c r="C5" s="30">
         <f>SUM(E9:E57)</f>
         <v>498</v>
       </c>
-      <c r="F5" s="53"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="55">
+      <c r="D5" s="30"/>
+      <c r="E5" s="34">
         <f>SUM(G9:G57)</f>
         <v>1031.3</v>
       </c>
-      <c r="I5" s="56"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="58">
+      <c r="F5" s="35"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="38">
         <f>SUM(H9:H57)</f>
         <v>3291.3</v>
       </c>
-      <c r="L5" s="59"/>
-      <c r="M5" s="59"/>
-      <c r="N5" s="60"/>
-    </row>
-    <row r="6" spans="1:14" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
+      <c r="I5" s="46"/>
+    </row>
+    <row r="6" spans="2:9" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
@@ -1043,971 +1006,626 @@
       <c r="I7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="3"/>
-    </row>
-    <row r="8" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:14" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5" t="s">
+    </row>
+    <row r="8" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="2:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E9" s="1">
         <v>218</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <v>30</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="7">
         <v>32.700000000000003</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <v>62.7</v>
       </c>
-      <c r="I9" s="37" t="s">
+      <c r="I9" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="38"/>
-      <c r="N9" s="38"/>
-    </row>
-    <row r="10" spans="1:14" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="10"/>
-      <c r="B10" s="11" t="s">
+    </row>
+    <row r="10" spans="2:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="11">
         <v>45</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="6">
         <v>180</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="7">
         <v>40.5</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="8">
         <v>220.5</v>
       </c>
-      <c r="I10" s="37" t="s">
+      <c r="I10" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="38"/>
-    </row>
-    <row r="11" spans="1:14" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5" t="s">
+    </row>
+    <row r="11" spans="2:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="2">
         <v>88</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="6">
         <v>500</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="7">
         <v>220</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="8">
         <v>720</v>
       </c>
-      <c r="I11" s="37" t="s">
+      <c r="I11" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-    </row>
-    <row r="12" spans="1:14" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11" t="s">
+    </row>
+    <row r="12" spans="2:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="9" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="10" t="s">
         <v>25</v>
       </c>
       <c r="E12" s="2">
         <v>113</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="6">
         <v>1200</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="7">
         <v>678.6</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="8">
         <v>1878.6</v>
       </c>
-      <c r="I12" s="37" t="s">
+      <c r="I12" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-    </row>
-    <row r="13" spans="1:14" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4"/>
-      <c r="B13" s="5" t="s">
+    </row>
+    <row r="13" spans="2:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="11">
         <v>34</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="6">
         <v>350</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="7">
         <v>59.5</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="8">
         <v>409.5</v>
       </c>
-      <c r="I13" s="37" t="s">
+      <c r="I13" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-    </row>
-    <row r="14" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="37"/>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="L14" s="38"/>
-      <c r="M14" s="38"/>
-      <c r="N14" s="38"/>
-    </row>
-    <row r="15" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="38"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="38"/>
-      <c r="N15" s="38"/>
-    </row>
-    <row r="16" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="10"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="38"/>
-    </row>
-    <row r="17" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-    </row>
-    <row r="18" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="10"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="38"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="38"/>
-    </row>
-    <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="37"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="38"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="38"/>
-      <c r="N19" s="38"/>
-    </row>
-    <row r="20" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="10"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="38"/>
-      <c r="L20" s="38"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="38"/>
-    </row>
-    <row r="21" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="38"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38"/>
-    </row>
-    <row r="22" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="10"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="38"/>
-    </row>
-    <row r="23" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-    </row>
-    <row r="24" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="10"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
-    </row>
-    <row r="25" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="4"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="38"/>
-      <c r="L25" s="38"/>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-    </row>
-    <row r="26" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="10"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="37"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="38"/>
-      <c r="L26" s="38"/>
-      <c r="M26" s="38"/>
-      <c r="N26" s="38"/>
-    </row>
-    <row r="27" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="4"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="38"/>
-      <c r="K27" s="38"/>
-      <c r="L27" s="38"/>
-      <c r="M27" s="38"/>
-      <c r="N27" s="38"/>
-    </row>
-    <row r="28" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="10"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
-    </row>
-    <row r="29" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="4"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="38"/>
-      <c r="K29" s="38"/>
-      <c r="L29" s="38"/>
-      <c r="M29" s="38"/>
-      <c r="N29" s="38"/>
-    </row>
-    <row r="30" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="10"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="37"/>
-      <c r="J30" s="38"/>
-      <c r="K30" s="38"/>
-      <c r="L30" s="38"/>
-      <c r="M30" s="38"/>
-      <c r="N30" s="38"/>
-    </row>
-    <row r="31" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="4"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="37"/>
-      <c r="J31" s="38"/>
-      <c r="K31" s="38"/>
-      <c r="L31" s="38"/>
-      <c r="M31" s="38"/>
-      <c r="N31" s="38"/>
-    </row>
-    <row r="32" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="10"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="37"/>
-      <c r="J32" s="38"/>
-      <c r="K32" s="38"/>
-      <c r="L32" s="38"/>
-      <c r="M32" s="38"/>
-      <c r="N32" s="38"/>
-    </row>
-    <row r="33" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="4"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="37"/>
-      <c r="J33" s="38"/>
-      <c r="K33" s="38"/>
-      <c r="L33" s="38"/>
-      <c r="M33" s="38"/>
-      <c r="N33" s="38"/>
-    </row>
-    <row r="34" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="10"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="37"/>
-      <c r="J34" s="38"/>
-      <c r="K34" s="38"/>
-      <c r="L34" s="38"/>
-      <c r="M34" s="38"/>
-      <c r="N34" s="38"/>
-    </row>
-    <row r="35" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="4"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="37"/>
-      <c r="J35" s="38"/>
-      <c r="K35" s="38"/>
-      <c r="L35" s="38"/>
-      <c r="M35" s="38"/>
-      <c r="N35" s="38"/>
-    </row>
-    <row r="36" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="10"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="37"/>
-      <c r="J36" s="38"/>
-      <c r="K36" s="38"/>
-      <c r="L36" s="38"/>
-      <c r="M36" s="38"/>
-      <c r="N36" s="38"/>
-    </row>
-    <row r="37" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="4"/>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="37"/>
-      <c r="J37" s="38"/>
-      <c r="K37" s="38"/>
-      <c r="L37" s="38"/>
-      <c r="M37" s="38"/>
-      <c r="N37" s="38"/>
-    </row>
-    <row r="38" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="10"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="37"/>
-      <c r="J38" s="38"/>
-      <c r="K38" s="38"/>
-      <c r="L38" s="38"/>
-      <c r="M38" s="38"/>
-      <c r="N38" s="38"/>
-    </row>
-    <row r="39" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="4"/>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="37"/>
-      <c r="J39" s="38"/>
-      <c r="K39" s="38"/>
-      <c r="L39" s="38"/>
-      <c r="M39" s="38"/>
-      <c r="N39" s="38"/>
-    </row>
-    <row r="40" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="10"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="37"/>
-      <c r="J40" s="38"/>
-      <c r="K40" s="38"/>
-      <c r="L40" s="38"/>
-      <c r="M40" s="38"/>
-      <c r="N40" s="38"/>
-    </row>
-    <row r="41" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="4"/>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
-      <c r="I41" s="37"/>
-      <c r="J41" s="38"/>
-      <c r="K41" s="38"/>
-      <c r="L41" s="38"/>
-      <c r="M41" s="38"/>
-      <c r="N41" s="38"/>
-    </row>
-    <row r="42" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="10"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="37"/>
-      <c r="J42" s="38"/>
-      <c r="K42" s="38"/>
-      <c r="L42" s="38"/>
-      <c r="M42" s="38"/>
-      <c r="N42" s="38"/>
-    </row>
-    <row r="43" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="4"/>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="37"/>
-      <c r="J43" s="38"/>
-      <c r="K43" s="38"/>
-      <c r="L43" s="38"/>
-      <c r="M43" s="38"/>
-      <c r="N43" s="38"/>
-    </row>
-    <row r="44" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="10"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="37"/>
-      <c r="J44" s="38"/>
-      <c r="K44" s="38"/>
-      <c r="L44" s="38"/>
-      <c r="M44" s="38"/>
-      <c r="N44" s="38"/>
-    </row>
-    <row r="45" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="4"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="37"/>
-      <c r="J45" s="38"/>
-      <c r="K45" s="38"/>
-      <c r="L45" s="38"/>
-      <c r="M45" s="38"/>
-      <c r="N45" s="38"/>
-    </row>
-    <row r="46" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="10"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="37"/>
-      <c r="J46" s="38"/>
-      <c r="K46" s="38"/>
-      <c r="L46" s="38"/>
-      <c r="M46" s="38"/>
-      <c r="N46" s="38"/>
-    </row>
-    <row r="47" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="4"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="37"/>
-      <c r="J47" s="38"/>
-      <c r="K47" s="38"/>
-      <c r="L47" s="38"/>
-      <c r="M47" s="38"/>
-      <c r="N47" s="38"/>
-    </row>
-    <row r="48" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="10"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="37"/>
-      <c r="J48" s="38"/>
-      <c r="K48" s="38"/>
-      <c r="L48" s="38"/>
-      <c r="M48" s="38"/>
-      <c r="N48" s="38"/>
-    </row>
-    <row r="49" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="4"/>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="37"/>
-      <c r="J49" s="38"/>
-      <c r="K49" s="38"/>
-      <c r="L49" s="38"/>
-      <c r="M49" s="38"/>
-      <c r="N49" s="38"/>
-    </row>
-    <row r="50" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="10"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="37"/>
-      <c r="J50" s="38"/>
-      <c r="K50" s="38"/>
-      <c r="L50" s="38"/>
-      <c r="M50" s="38"/>
-      <c r="N50" s="38"/>
-    </row>
-    <row r="51" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="4"/>
-      <c r="B51" s="15"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="15"/>
-      <c r="I51" s="37"/>
-      <c r="J51" s="38"/>
-      <c r="K51" s="38"/>
-      <c r="L51" s="38"/>
-      <c r="M51" s="38"/>
-      <c r="N51" s="38"/>
-    </row>
-    <row r="52" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="10"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="37"/>
-      <c r="J52" s="38"/>
-      <c r="K52" s="38"/>
-      <c r="L52" s="38"/>
-      <c r="M52" s="38"/>
-      <c r="N52" s="38"/>
-    </row>
-    <row r="53" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="4"/>
-      <c r="B53" s="15"/>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="15"/>
-      <c r="I53" s="37"/>
-      <c r="J53" s="38"/>
-      <c r="K53" s="38"/>
-      <c r="L53" s="38"/>
-      <c r="M53" s="38"/>
-      <c r="N53" s="38"/>
-    </row>
-    <row r="54" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="10"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="37"/>
-      <c r="J54" s="38"/>
-      <c r="K54" s="38"/>
-      <c r="L54" s="38"/>
-      <c r="M54" s="38"/>
-      <c r="N54" s="38"/>
-    </row>
-    <row r="55" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="4"/>
-      <c r="B55" s="15"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="15"/>
-      <c r="H55" s="15"/>
-      <c r="I55" s="37"/>
-      <c r="J55" s="38"/>
-      <c r="K55" s="38"/>
-      <c r="L55" s="38"/>
-      <c r="M55" s="38"/>
-      <c r="N55" s="38"/>
-    </row>
-    <row r="56" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="10"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="37"/>
-      <c r="J56" s="38"/>
-      <c r="K56" s="38"/>
-      <c r="L56" s="38"/>
-      <c r="M56" s="38"/>
-      <c r="N56" s="38"/>
-    </row>
-    <row r="57" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="4"/>
-      <c r="B57" s="15"/>
-      <c r="C57" s="15"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="15"/>
-      <c r="I57" s="37"/>
-      <c r="J57" s="38"/>
-      <c r="K57" s="38"/>
-      <c r="L57" s="38"/>
-      <c r="M57" s="38"/>
-      <c r="N57" s="38"/>
-    </row>
-    <row r="58" spans="1:14" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="35" t="s">
+    </row>
+    <row r="14" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="48"/>
+    </row>
+    <row r="15" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="48"/>
+    </row>
+    <row r="16" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="48"/>
+    </row>
+    <row r="17" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="48"/>
+    </row>
+    <row r="18" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="48"/>
+    </row>
+    <row r="19" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="48"/>
+    </row>
+    <row r="20" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="48"/>
+    </row>
+    <row r="21" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="48"/>
+    </row>
+    <row r="22" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="48"/>
+    </row>
+    <row r="23" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="48"/>
+    </row>
+    <row r="24" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="48"/>
+    </row>
+    <row r="25" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="48"/>
+    </row>
+    <row r="26" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="48"/>
+    </row>
+    <row r="27" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="48"/>
+    </row>
+    <row r="28" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="48"/>
+    </row>
+    <row r="29" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="48"/>
+    </row>
+    <row r="30" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="48"/>
+    </row>
+    <row r="31" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="48"/>
+    </row>
+    <row r="32" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="48"/>
+    </row>
+    <row r="33" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="48"/>
+    </row>
+    <row r="34" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="48"/>
+    </row>
+    <row r="35" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="48"/>
+    </row>
+    <row r="36" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="48"/>
+    </row>
+    <row r="37" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="48"/>
+    </row>
+    <row r="38" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="48"/>
+    </row>
+    <row r="39" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="48"/>
+    </row>
+    <row r="40" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="48"/>
+    </row>
+    <row r="41" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="48"/>
+    </row>
+    <row r="42" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+      <c r="I42" s="48"/>
+    </row>
+    <row r="43" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="48"/>
+    </row>
+    <row r="44" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="48"/>
+    </row>
+    <row r="45" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="48"/>
+    </row>
+    <row r="46" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="48"/>
+    </row>
+    <row r="47" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="48"/>
+    </row>
+    <row r="48" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="48"/>
+    </row>
+    <row r="49" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="48"/>
+    </row>
+    <row r="50" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="48"/>
+    </row>
+    <row r="51" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="48"/>
+    </row>
+    <row r="52" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+      <c r="I52" s="48"/>
+    </row>
+    <row r="53" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="48"/>
+    </row>
+    <row r="54" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="48"/>
+    </row>
+    <row r="55" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="48"/>
+    </row>
+    <row r="56" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+      <c r="I56" s="48"/>
+    </row>
+    <row r="57" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="48"/>
+    </row>
+    <row r="58" spans="2:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="33"/>
-      <c r="D58" s="33"/>
-      <c r="E58" s="33"/>
-      <c r="F58" s="16">
+      <c r="C58" s="42"/>
+      <c r="D58" s="42"/>
+      <c r="E58" s="42"/>
+      <c r="F58" s="14">
         <f>SUM(F9:F57)</f>
         <v>2260</v>
       </c>
-      <c r="G58" s="16">
+      <c r="G58" s="14">
         <f>SUM(G9:G57)</f>
         <v>1031.3</v>
       </c>
-      <c r="H58" s="16">
+      <c r="H58" s="14">
         <f>SUM(H9:H57)</f>
         <v>3291.3</v>
       </c>
-      <c r="I58" s="17"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B60" s="32" t="s">
+      <c r="I58" s="15"/>
+    </row>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B60" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="C60" s="33"/>
-      <c r="D60" s="33"/>
-      <c r="E60" s="33"/>
-      <c r="F60" s="33"/>
-      <c r="G60" s="33"/>
-      <c r="H60" s="33"/>
-      <c r="I60" s="33"/>
+      <c r="C60" s="42"/>
+      <c r="D60" s="42"/>
+      <c r="E60" s="42"/>
+      <c r="F60" s="42"/>
+      <c r="G60" s="42"/>
+      <c r="H60" s="42"/>
+      <c r="I60" s="42"/>
     </row>
   </sheetData>
-  <mergeCells count="61">
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="I53:N53"/>
-    <mergeCell ref="I54:N54"/>
-    <mergeCell ref="I55:N55"/>
-    <mergeCell ref="I56:N56"/>
-    <mergeCell ref="I57:N57"/>
-    <mergeCell ref="I48:N48"/>
-    <mergeCell ref="I49:N49"/>
-    <mergeCell ref="I50:N50"/>
-    <mergeCell ref="I51:N51"/>
-    <mergeCell ref="I52:N52"/>
-    <mergeCell ref="I43:N43"/>
-    <mergeCell ref="I44:N44"/>
-    <mergeCell ref="I45:N45"/>
-    <mergeCell ref="I46:N46"/>
-    <mergeCell ref="I47:N47"/>
-    <mergeCell ref="I38:N38"/>
-    <mergeCell ref="I39:N39"/>
-    <mergeCell ref="I40:N40"/>
-    <mergeCell ref="I41:N41"/>
-    <mergeCell ref="I42:N42"/>
-    <mergeCell ref="I33:N33"/>
-    <mergeCell ref="I34:N34"/>
-    <mergeCell ref="I35:N35"/>
-    <mergeCell ref="I36:N36"/>
-    <mergeCell ref="I37:N37"/>
-    <mergeCell ref="I28:N28"/>
-    <mergeCell ref="I29:N29"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="I31:N31"/>
-    <mergeCell ref="I32:N32"/>
-    <mergeCell ref="I23:N23"/>
-    <mergeCell ref="I24:N24"/>
-    <mergeCell ref="I25:N25"/>
-    <mergeCell ref="I26:N26"/>
-    <mergeCell ref="I27:N27"/>
-    <mergeCell ref="I18:N18"/>
-    <mergeCell ref="I19:N19"/>
-    <mergeCell ref="I20:N20"/>
-    <mergeCell ref="I21:N21"/>
-    <mergeCell ref="I22:N22"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B3:N3"/>
+  <mergeCells count="10">
+    <mergeCell ref="B60:I60"/>
+    <mergeCell ref="B58:E58"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C5:D5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="E4:G4"/>
-    <mergeCell ref="B60:I60"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="I9:N9"/>
-    <mergeCell ref="I10:N10"/>
-    <mergeCell ref="I11:N11"/>
-    <mergeCell ref="I12:N12"/>
-    <mergeCell ref="I13:N13"/>
-    <mergeCell ref="I14:N14"/>
-    <mergeCell ref="I15:N15"/>
-    <mergeCell ref="I16:N16"/>
-    <mergeCell ref="I17:N17"/>
+    <mergeCell ref="E5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2027,43 +1645,43 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="4" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18" t="s">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="18"/>
+      <c r="I4" s="16"/>
     </row>
     <row r="6" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="17" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -2072,46 +1690,46 @@
       <c r="D6" s="1">
         <v>218</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="6">
         <v>30</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="7">
         <v>32.700000000000003</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8">
         <f>F6+G6</f>
         <v>62.7</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="19" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="11">
         <v>45</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <v>180</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="7">
         <v>40.5</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8">
         <f>F7+G7</f>
         <v>220.5</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="17" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -2120,22 +1738,22 @@
       <c r="D8" s="2">
         <v>88</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <v>500</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="7">
         <v>220</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="8">
         <f>F8+G8</f>
         <v>720</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="19" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -2144,60 +1762,60 @@
       <c r="D9" s="2">
         <v>113</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <v>1200</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="7">
         <v>678.6</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <f>F9+G9</f>
         <v>1878.6</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="17" t="s">
         <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="11">
         <v>34</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="6">
         <v>350</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="7">
         <v>59.5</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="8">
         <f>F10+G10</f>
         <v>409.5</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="16">
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="14">
         <f>SUM(F6:F11)</f>
         <v>2260</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="14">
         <f>SUM(G6:G11)</f>
         <v>1031.3</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="14">
         <f>SUM(H6:H11)</f>
         <v>3291.3</v>
       </c>
@@ -2224,209 +1842,209 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
     </row>
     <row r="4" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18" t="s">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="18"/>
+      <c r="G4" s="16"/>
     </row>
     <row r="6" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="21">
         <v>0</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="6">
         <v>0</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <v>0</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="8">
         <f t="shared" ref="F6:F14" si="0">D6+E6</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="21">
         <v>0</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>0</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="7">
         <v>0</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="21">
         <v>0</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <v>0</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="7">
         <v>0</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="21">
         <v>0</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="6">
         <v>0</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="7">
         <v>0</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="21">
         <v>0</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>0</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="7">
         <v>0</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="21">
         <v>1</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>350</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <v>59.5</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="8">
         <f t="shared" si="0"/>
         <v>409.5</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="21">
         <v>1</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>1200</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="7">
         <v>678.6</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="8">
         <f t="shared" si="0"/>
         <v>1878.6</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="21">
         <v>1</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="6">
         <v>500</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="7">
         <v>220</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="8">
         <f t="shared" si="0"/>
         <v>720</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="21">
         <v>3</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <v>210</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="7">
         <v>73.2</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="8">
         <f t="shared" si="0"/>
         <v>283.2</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="35" t="s">
+      <c r="B16" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="16">
+      <c r="C16" s="42"/>
+      <c r="D16" s="14">
         <f>SUM(D6:D15)</f>
         <v>2260</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="14">
         <f>SUM(E6:E15)</f>
         <v>1031.3</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="14">
         <f>SUM(F6:F15)</f>
         <v>3291.2999999999997</v>
       </c>
